--- a/data_extactor/batch_10_fa/trimmed/batch_0041_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0041_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | زبان‌های خارجی | خدمات مشتریان و خدمات فردی | آموزش و پرورش | امور اداری و دفتری | ایمنی و امنیت عمومی | حقوق و امور دولتی</t>
+          <t>زبان انگلیسی | زبان خارجی | خدمات مشتری و شخصی | آموزش و پرورش | اداری | ایمنی و امنیت عمومی | قانون و دولت</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مربیان آموزش پایه بزرگسالان، آموزش متوسطه بزرگسالان و آموزش زبان انگلیسی به عنوان زبان دوم | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان زبان و ادبیات خارجی در دانشگاه‌ها و مراکز آموزش عالی | نمونه‌خوانان و تصحیح‌کنندگان متون چاپی | گفتاردرمانگران | نویسندگان متون فنی و تخصصی | تایپیست‌ها و متصدیان پردازش متن</t>
+          <t>مربیان سوادآموزی بزرگسالان، دوره اول و دوم متوسطه بزرگسالان و زبان دوم | مدرسان زبان و ادبیات انگلیسی در دانشگاه‌ها و مراکز آموزش عالی | مدرسان زبان و ادبیات خارجی در دانشگاه‌ها و مراکز آموزش عالی | ویراستاران فنی و نمونه‌خوان‌ها | آسیب‌شناسان گفتار و زبان / گفتاردرمانگران | نویسندگان متون فنی | تایپیست‌ها و متصدیان حروف‌چینی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نگارش | درک مطلب | نظارت | سخن گفتن</t>
+          <t>گوش دادن فعال | نگارش | درک مطلب | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | امور اداری و دفتری | کامپیوتر و الکترونیک | حقوق و امور دولتی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | ارتباطات و رسانه</t>
+          <t>زبان انگلیسی | اداری | رایانه و الکترونیک | قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | تشخیص گفتار | بیان کتبی | درک کتبی | دید نزدیک | توجه انتخابی | سرعت مچ و انگشتان</t>
+          <t>درک شفاهی | تشخیص گفتار | بیان کتبی | درک کتبی | بینایی نزدیک | توجه انتخابی | سرعت مچ و انگشتان</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کارمندان دادگاه، شهرداری و صدور پروانه | متصدیان ورود اطلاعات | داد‌یاران و کارشناسان حقوقی قضایی | مسئولان دفاتر و دستیاران امور حقوقی | پیاده‌سازان متون پزشکی | کارشناسان امور حقوقی و دستیاران وکالت | تایپیست‌ها و متصدیان پردازش متن</t>
+          <t>کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | متصدیان ورود اطلاعات و داده‌آمایی | کارشناسان پژوهش و تحریر قضایی | منشی‌ها و دستیاران اداری دفاتر حقوقی | پیاده‌سازان و تایپیست‌های متون پزشکی | کارشناسان و دستیاران امور حقوقی | تایپیست‌ها و متصدیان حروف‌چینی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | زبان انگلیسی | کامپیوتر و الکترونیک | فروش و بازاریابی | خدمات مشتریان و خدمات فردی | هنرهای تجسمی</t>
+          <t>ارتباطات و رسانه | زبان انگلیسی | رایانه و الکترونیک | فروش و بازاریابی | خدمات مشتری و شخصی | هنرهای زیبا</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | تفکر انتقادی | سخن گفتن | شنیدن فعال | نگارش | یادگیری فعال</t>
+          <t>نظارت | درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | مخابرات | مهندسی و فناوری | خدمات مشتریان و خدمات فردی</t>
+          <t>رایانه و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | مخابرات | مهندسی و فناوری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>دید نزدیک | بیان شفاهی | درک شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | درک کتبی | حساسیت شنوایی</t>
+          <t>بینایی نزدیک | بیان شفاهی | درک شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک کتبی | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>نصاب‌ها و تعمیرکاران تجهیزات سمعی و بصری | تکنسین‌های پخش | تصویربرداران تلویزیون، ویدیو و سینما | کاردان‌های فنی و تکنسین‌های مهندسی برق و الکترونیک | تکنسین‌های نورپردازی | تکنسین‌های مهندسی صدا | نصاب‌ها و تعمیرکاران تجهیزات مخابراتی، به جز خطوط ارتباطی</t>
+          <t>نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین‌های پخش و اتاق فرمان | تصویربرداران تلویزیون، ویدیو و سینما | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تکنسین‌های نورپردازی | تکنسین‌های مهندسی صدا | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | نظارت | نگارش | درک مطلب | سخن گفتن | یادگیری فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | نگارش | درک مطلب | سخن گفتن | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مخابرات | مهندسی و فناوری | ارتباطات و رسانه | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | مخابرات | مهندسی و فناوری | ارتباطات و رسانه | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>بینایی نزدیک | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین‌های تجهیزات صوتی و تصویری | نصاب‌ها و تعمیرکاران تجهیزات سمعی و بصری | تصویربرداران تلویزیون، ویدیو و سینما | کاردان‌های فنی و تکنسین‌های مهندسی برق و الکترونیک | تکنسین‌های نورپردازی | مدیران فنی رسانه | تکنسین‌های مهندسی صدا</t>
+          <t>تکنسین‌های تجهیزات صوتی و تصویری | نصاب و تعمیرکار تجهیزات صوتی و تصویری | تصویربرداران تلویزیون، ویدیو و سینما | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تکنسین‌های نورپردازی | مدیران فنی رسانه | تکنسین‌های مهندسی صدا</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | خدمات مشتریان و خدمات فردی | هنرهای تجسمی | زبان انگلیسی | مهندسی و فناوری | ارتباطات و رسانه | تولید و فرآوری</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | هنرهای زیبا | زبان انگلیسی | مهندسی و فناوری | ارتباطات و رسانه | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت شنوایی | درک شفاهی | بیان شفاهی | دید نزدیک | توجه شنیداری | توجه انتخابی | استدلال قیاسی</t>
+          <t>حساسیت شنوایی | درک شفاهی | بیان شفاهی | بینایی نزدیک | توجه شنیداری | توجه انتخابی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های تجهیزات صوتی و تصویری | تکنسین‌های پخش | تصویربرداران تلویزیون، ویدیو و سینما | تدوین‌گران فیلم و ویدیو | مدیران فنی رسانه | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | تهیه‌کنندگان و کارگردانان</t>
+          <t>تکنسین‌های تجهیزات صوتی و تصویری | تکنسین‌های پخش و اتاق فرمان | تصویربرداران تلویزیون، ویدیو و سینما | تدوین‌گران فیلم و ویدیو | مدیران فنی رسانه | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | تهیه‌کنندگان و کارگردانان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | هنرهای تجسمی | مهندسی و فناوری | ارتباطات و رسانه | طراحی | ایمنی و امنیت عمومی</t>
+          <t>رایانه و الکترونیک | هنرهای زیبا | مهندسی و فناوری | ارتباطات و رسانه | طراحی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | دید نزدیک | چابکی دستی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | حساسیت به مسئله | بینایی نزدیک | مهارت دستی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کاردان‌های فنی و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | برق‌کاران | کارگران کمکی برق‌کاران | کارگران عمومی تعمیرات و نگهداری | نصاب‌های سیستم‌های امنیتی و اعلام حریق</t>
+          <t>کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | برق‌کاران | کمک‌برق‌کاران | کارگران عمومی تعمیرات و نگهداری تاسیسات | نصاب سیستم‌های اعلام سرقت و حریق</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فروش و بازاریابی | کامپیوتر و الکترونیک | مدیریت و امور اداری | ارتباطات و رسانه | هنرهای تجسمی</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | رایانه و الکترونیک | مدیریت و اداره | ارتباطات و رسانه | هنرهای زیبا</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | بیان شفاهی | ابتکار | تجسم فضایی | دید دور | تشخیص رنگ | درک شفاهی</t>
+          <t>بینایی نزدیک | بیان شفاهی | اصالت | تجسم | بینایی دور | تشخیص رنگ بصری | درک شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تصویربرداران تلویزیون، ویدیو و سینما | تعمیرکاران دوربین و تجهیزات عکاسی | تدوین‌گران فیلم و ویدیو | طراحان گرافیک | چیدمان‌کنندگان کالا و طراحان ویترین | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های چاپ عکس | تهیه‌کنندگان و کارگردانان</t>
+          <t>تصویربرداران تلویزیون، ویدیو و سینما | تعمیرکاران دوربین و تجهیزات عکاسی | تدوین‌گران فیلم و ویدیو | طراحان گرافیک | طراحان دکوراسیون و ویترین مغازه | کارگران و اپراتورهای ماشین‌های فرآوری و چاپ عکس | تهیه‌کنندگان و کارگردانان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | کامپیوتر و الکترونیک | ارتباطات و رسانه | مخابرات</t>
+          <t>زبان انگلیسی | رایانه و الکترونیک | ارتباطات و رسانه | مخابرات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>تجسم فضایی | دید نزدیک | دید دور | بیان شفاهی | حساسیت به مسئله | درک شفاهی | تشخیص رنگ</t>
+          <t>تجسم | بینایی نزدیک | بینایی دور | بیان شفاهی | حساسیت به مسئله | درک شفاهی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تکنسین‌های تجهیزات صوتی و تصویری | تکنسین‌های پخش | تعمیرکاران دوربین و تجهیزات عکاسی | تدوین‌گران فیلم و ویدیو | تکنسین‌های نورپردازی | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا</t>
+          <t>تکنسین‌های تجهیزات صوتی و تصویری | تکنسین‌های پخش و اتاق فرمان | تعمیرکاران دوربین و تجهیزات عکاسی | تدوین‌گران فیلم و ویدیو | تکنسین‌های نورپردازی | تهیه‌کنندگان و کارگردانان | تکنسین‌های مهندسی صدا</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | سخن گفتن | نگارش | نظارت</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | سخن گفتن | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ارتباطات و رسانه | زبان انگلیسی | کامپیوتر و الکترونیک | هنرهای تجسمی | تولید و فرآوری | طراحی</t>
+          <t>ارتباطات و رسانه | زبان انگلیسی | رایانه و الکترونیک | هنرهای زیبا | تولید و فرآوری | طراحی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | دید نزدیک | بیان شفاهی | مرتب‌سازی اطلاعات | تجسم فضایی | روانی ایده‌ها | ابتکار</t>
+          <t>درک شفاهی | بینایی نزدیک | بیان شفاهی | ترتیب‌دهی اطلاعات | تجسم | روانی ایده‌ها | اصالت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های تجهیزات صوتی و تصویری | تصویربرداران تلویزیون، ویدیو و سینما | ویراستاران | طراحان گرافیک | عکاسان | تهیه‌کنندگان و کارگردانان | هنرمندان جلوه‌های ویژه و پویانماها</t>
+          <t>تکنسین‌های تجهیزات صوتی و تصویری | تصویربرداران تلویزیون، ویدیو و سینما | ویراستاران | طراحان گرافیک | عکاسان | تهیه‌کنندگان و کارگردانان | پویانماها و طراحان جلوه‌های ویژه</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
